--- a/Capitulos/APENDICE A-4-Tabla Municipios.xlsx
+++ b/Capitulos/APENDICE A-4-Tabla Municipios.xlsx
@@ -8,31 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\NSR-10\Capitulos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E090FB13-74CE-47B8-B273-FDBB4B6781A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C0407F-6EF1-4CC0-A694-B97ADE2B1C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{12BF304A-4D71-42C4-ABF0-AA4BA6655E39}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{12BF304A-4D71-42C4-ABF0-AA4BA6655E39}"/>
   </bookViews>
   <sheets>
     <sheet name="BD_Municipios" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Aa">[1]ESPECTRO_NSR10!$B$6</definedName>
-    <definedName name="AaARM">'[1]Micro_Armenia (Y)'!$B$8</definedName>
-    <definedName name="AaBOG">[1]Micro_Bogotá_ESPEC!$H$9</definedName>
-    <definedName name="AaPER">[1]Micro_Pereira!$B$8</definedName>
-    <definedName name="alpha">[1]INICIO!$E$46</definedName>
     <definedName name="Amazonas">BD_Municipios!$A$3:$A$13</definedName>
     <definedName name="Antioquia">BD_Municipios!$A$15:$A$139</definedName>
-    <definedName name="Ao">[1]Micro_Bogotá_ESPEC!$B$9</definedName>
-    <definedName name="AoBOG">[1]Micro_Bogotá_ESPEC!$B$9</definedName>
     <definedName name="Arauca">BD_Municipios!$A$141:$A$147</definedName>
     <definedName name="Atlántico">BD_Municipios!$A$152:$A$174</definedName>
-    <definedName name="Av">[1]ESPECTRO_NSR10!$B$7</definedName>
-    <definedName name="AvBOG">[1]Micro_Bogotá_ESPEC!$H$10</definedName>
     <definedName name="Bolívar">BD_Municipios!$A$176:$A$220</definedName>
     <definedName name="Boyacá">BD_Municipios!$A$222:$A$344</definedName>
     <definedName name="Caldas">BD_Municipios!$A$346:$A$372</definedName>
@@ -42,67 +29,27 @@
     <definedName name="Cesar">BD_Municipios!$A$453:$A$477</definedName>
     <definedName name="Chocó">BD_Municipios!$A$479:$A$509</definedName>
     <definedName name="Córdoba">BD_Municipios!$A$511:$A$538</definedName>
-    <definedName name="Ct">[1]INICIO!$E$45</definedName>
     <definedName name="Cundinamarca">BD_Municipios!$A$540:$A$656</definedName>
     <definedName name="Departamento">BD_Municipios!$L$2:$L$34</definedName>
     <definedName name="Distrito">BD_Municipios!$A$658</definedName>
-    <definedName name="espectral">'[2]4-Matriz espectral'!$B$2:$E$5</definedName>
-    <definedName name="Fa">[1]ESPECTRO_NSR10!$B$8</definedName>
-    <definedName name="FaARM">'[1]Micro_Armenia (Y)'!$B$9</definedName>
-    <definedName name="FaBOG">[1]Micro_Bogotá_ESPEC!$B$10</definedName>
-    <definedName name="Fap">[1]ESPECTRO_CCP2014!$F$6</definedName>
-    <definedName name="FaPER">[1]Micro_Pereira!$B$9</definedName>
-    <definedName name="Fpga">[1]ESPECTRO_CCP2014!$F$5</definedName>
-    <definedName name="Fv">[1]ESPECTRO_NSR10!$B$9</definedName>
-    <definedName name="FvARM">'[1]Micro_Armenia (Y)'!$B$10</definedName>
-    <definedName name="FvBOG">[1]Micro_Bogotá_ESPEC!$B$11</definedName>
-    <definedName name="Fvp">[1]ESPECTRO_CCP2014!$F$7</definedName>
-    <definedName name="FvPER">[1]Micro_Pereira!$B$10</definedName>
-    <definedName name="GAMAmod">'[2]9-GAMA'!$B$1:$E$4</definedName>
     <definedName name="Guainía">BD_Municipios!$A$660:$A$668</definedName>
     <definedName name="Guaviare">BD_Municipios!$A$686:$A$689</definedName>
     <definedName name="Huila">BD_Municipios!$A$691:$A$727</definedName>
-    <definedName name="I">[1]ESPECTRO_NSR10!$B$10</definedName>
-    <definedName name="IBOG">[1]Micro_Bogotá_ESPEC!$E$11</definedName>
-    <definedName name="IDER">#REF!</definedName>
-    <definedName name="L">[1]INICIO!$B$17</definedName>
     <definedName name="La_Guajira">BD_Municipios!$A$670:$A$684</definedName>
-    <definedName name="M">'[2]2-Matriz de masas'!$B$3:$E$6</definedName>
     <definedName name="Magdalena">BD_Municipios!$A$729:$A$758</definedName>
     <definedName name="Meta">BD_Municipios!$A$760:$A$788</definedName>
-    <definedName name="modal">'[2]3-Matriz modal'!$B$3:$E$6</definedName>
-    <definedName name="modalT">'[2]3-Matriz modal'!$B$10:$E$13</definedName>
     <definedName name="Nariño">BD_Municipios!$A$790:$A$852</definedName>
     <definedName name="Norte_De_Santander">BD_Municipios!$A$854:$A$893</definedName>
-    <definedName name="PGA">[1]ESPECTRO_CCP2014!$B$5</definedName>
     <definedName name="Putumayo">BD_Municipios!$A$895:$A$907</definedName>
     <definedName name="Quindío">BD_Municipios!$A$909:$A$920</definedName>
     <definedName name="Risaralda">BD_Municipios!$A$922:$A$935</definedName>
-    <definedName name="Rsis">'[1]CORTANTE BASAL (Y)'!$B$6</definedName>
-    <definedName name="S_1">[1]ESPECTRO_CCP2014!$B$7</definedName>
-    <definedName name="Sa">[1]Micro_Bogotá_ESPEC!$B$15:$B$50</definedName>
     <definedName name="San_Andrés">BD_Municipios!$A$149:$A$150</definedName>
     <definedName name="Santander">BD_Municipios!$A$937:$A$1023</definedName>
-    <definedName name="Sared">[1]Micro_Bogotá_ESPEC!$D$15:$D$50</definedName>
-    <definedName name="Sd">'[2]7-PERIODO'!$F$4:$F$7</definedName>
-    <definedName name="Ss">[1]ESPECTRO_CCP2014!$B$6</definedName>
     <definedName name="Sucre">BD_Municipios!$A$1025:$A$1049</definedName>
-    <definedName name="T">[1]ESPECTRO_NSR10!$A$13:$A$65</definedName>
-    <definedName name="TBOG">[1]Micro_Bogotá_ESPEC!$A$15:$A$50</definedName>
-    <definedName name="Tc">[1]ESPECTRO_NSR10!$E$9</definedName>
-    <definedName name="TcBOG">[1]Micro_Bogotá_ESPEC!$E$9</definedName>
-    <definedName name="temp">[2]ModalxM!$B$1:$E$4</definedName>
-    <definedName name="Tl">[1]ESPECTRO_NSR10!$E$10</definedName>
-    <definedName name="TlBOG">[1]Micro_Bogotá_ESPEC!$E$10</definedName>
-    <definedName name="To">[1]ESPECTRO_NSR10!$E$8</definedName>
     <definedName name="Tolima">BD_Municipios!$A$1051:$A$1097</definedName>
-    <definedName name="Top">[1]ESPECTRO_CCP2014!$I$5</definedName>
-    <definedName name="Tsp">[1]ESPECTRO_CCP2014!$I$6</definedName>
-    <definedName name="Umod">'[2]10-Desp+Deriva'!$B$2:$E$5</definedName>
     <definedName name="Valle">BD_Municipios!$A$1099:$A$1140</definedName>
     <definedName name="Vaupés">BD_Municipios!$A$1142:$A$1147</definedName>
     <definedName name="Vichada">BD_Municipios!$A$1149:$A$1152</definedName>
-    <definedName name="W">[1]INICIO!$B$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4408,1376 +4355,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="CONTENIDO"/>
-      <sheetName val="INICIO"/>
-      <sheetName val="BASE"/>
-      <sheetName val="EvCargas PISO"/>
-      <sheetName val="EvCargas CUBIERTA"/>
-      <sheetName val="EvCargas W -CUB-A"/>
-      <sheetName val="EvCargas W -CUB-B"/>
-      <sheetName val="CORTANTE BASAL (Y)"/>
-      <sheetName val="CORTANTE BASAL (X)"/>
-      <sheetName val="ESPECTRO_NSR10"/>
-      <sheetName val="Micro_Armenia (Y)"/>
-      <sheetName val="Micro_Armenia (X)"/>
-      <sheetName val="ESPECTRO_CCP2014"/>
-      <sheetName val="Micro_Bogotá_ESPEC"/>
-      <sheetName val="Micro_Pereira"/>
-      <sheetName val="BD_Municipios"/>
-      <sheetName val="DERIVAS"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="16">
-          <cell r="B16">
-            <v>7.7</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>8.9</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="E45">
-            <v>0.02</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="E46">
-            <v>0.75</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7">
-        <row r="6">
-          <cell r="B6">
-            <v>1.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9">
-        <row r="6">
-          <cell r="B6">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>1.45</v>
-          </cell>
-          <cell r="E8">
-            <v>0.20689655172413796</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>3</v>
-          </cell>
-          <cell r="E9">
-            <v>0.99310344827586206</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>1</v>
-          </cell>
-          <cell r="E10">
-            <v>7.1999999999999993</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>0.20689655172413796</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>0.99310344827586206</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>1.1000000000000001</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>1.2000000000000002</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>1.3000000000000003</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>1.4000000000000004</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>1.5000000000000004</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>1.6000000000000005</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>1.7000000000000006</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>1.8000000000000007</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>1.9000000000000008</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>2.0000000000000009</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>2.100000000000001</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>2.2000000000000011</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>2.3000000000000012</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>2.4000000000000012</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>2.5000000000000013</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>2.6000000000000014</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>2.7000000000000015</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>2.8000000000000016</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>2.9000000000000017</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>3.0000000000000018</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>3.1000000000000019</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>3.200000000000002</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>3.300000000000002</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>3.4000000000000021</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>3.5000000000000022</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>3.6000000000000023</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>3.7000000000000024</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>3.8000000000000025</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>3.9000000000000026</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>4.0000000000000027</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>4.1000000000000023</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>4.200000000000002</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>4.3000000000000016</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>4.4000000000000012</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>4.5000000000000009</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>4.6000000000000005</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>4.7</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>4.8</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>4.8999999999999995</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>4.9999999999999991</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>5.0999999999999988</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>5.1999999999999984</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>5.299999999999998</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>5.3999999999999977</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>5.4999999999999973</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>5.599999999999997</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>5.6999999999999966</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>5.7999999999999963</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>5.8999999999999959</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10">
-        <row r="8">
-          <cell r="B8">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>1.76</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>2.63</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12">
-        <row r="5">
-          <cell r="B5">
-            <v>0.25</v>
-          </cell>
-          <cell r="F5">
-            <v>1.2999999999999998</v>
-          </cell>
-          <cell r="I5">
-            <v>0.14615384615384616</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>0.6</v>
-          </cell>
-          <cell r="F6">
-            <v>1.2999999999999998</v>
-          </cell>
-          <cell r="I6">
-            <v>0.73076923076923084</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>0.3</v>
-          </cell>
-          <cell r="F7">
-            <v>1.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13">
-        <row r="9">
-          <cell r="B9">
-            <v>0.16</v>
-          </cell>
-          <cell r="E9">
-            <v>1.77</v>
-          </cell>
-          <cell r="H9">
-            <v>0.15</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>1.05</v>
-          </cell>
-          <cell r="E10">
-            <v>5</v>
-          </cell>
-          <cell r="H10">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>2.9</v>
-          </cell>
-          <cell r="E11">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>0</v>
-          </cell>
-          <cell r="B15">
-            <v>0.39375000000000004</v>
-          </cell>
-          <cell r="D15">
-            <v>0.39375000000000004</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>0.16</v>
-          </cell>
-          <cell r="B16">
-            <v>0.39375000000000004</v>
-          </cell>
-          <cell r="D16">
-            <v>0.26250000000000001</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>1.77</v>
-          </cell>
-          <cell r="B17">
-            <v>0.39375000000000004</v>
-          </cell>
-          <cell r="D17">
-            <v>0.26250000000000001</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>1.8</v>
-          </cell>
-          <cell r="B18">
-            <v>0.3866666666666666</v>
-          </cell>
-          <cell r="D18">
-            <v>0.25777777777777772</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>1.9000000000000001</v>
-          </cell>
-          <cell r="B19">
-            <v>0.36631578947368415</v>
-          </cell>
-          <cell r="D19">
-            <v>0.24421052631578943</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>2</v>
-          </cell>
-          <cell r="B20">
-            <v>0.34799999999999998</v>
-          </cell>
-          <cell r="D20">
-            <v>0.23199999999999998</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>2.1</v>
-          </cell>
-          <cell r="B21">
-            <v>0.33142857142857141</v>
-          </cell>
-          <cell r="D21">
-            <v>0.22095238095238093</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>2.2000000000000002</v>
-          </cell>
-          <cell r="B22">
-            <v>0.31636363636363629</v>
-          </cell>
-          <cell r="D22">
-            <v>0.21090909090909085</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>2.3000000000000003</v>
-          </cell>
-          <cell r="B23">
-            <v>0.30260869565217385</v>
-          </cell>
-          <cell r="D23">
-            <v>0.20173913043478256</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>2.4000000000000004</v>
-          </cell>
-          <cell r="B24">
-            <v>0.28999999999999992</v>
-          </cell>
-          <cell r="D24">
-            <v>0.19333333333333327</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>2.5000000000000004</v>
-          </cell>
-          <cell r="B25">
-            <v>0.27839999999999993</v>
-          </cell>
-          <cell r="D25">
-            <v>0.18559999999999996</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>2.6000000000000005</v>
-          </cell>
-          <cell r="B26">
-            <v>0.26769230769230762</v>
-          </cell>
-          <cell r="D26">
-            <v>0.17846153846153842</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>2.7000000000000006</v>
-          </cell>
-          <cell r="B27">
-            <v>0.25777777777777772</v>
-          </cell>
-          <cell r="D27">
-            <v>0.17185185185185181</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>2.8000000000000007</v>
-          </cell>
-          <cell r="B28">
-            <v>0.2485714285714285</v>
-          </cell>
-          <cell r="D28">
-            <v>0.16571428571428568</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>2.9000000000000008</v>
-          </cell>
-          <cell r="B29">
-            <v>0.23999999999999991</v>
-          </cell>
-          <cell r="D29">
-            <v>0.15999999999999995</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>3.0000000000000009</v>
-          </cell>
-          <cell r="B30">
-            <v>0.23199999999999993</v>
-          </cell>
-          <cell r="D30">
-            <v>0.15466666666666662</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>3.100000000000001</v>
-          </cell>
-          <cell r="B31">
-            <v>0.22451612903225798</v>
-          </cell>
-          <cell r="D31">
-            <v>0.14967741935483866</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>3.2000000000000011</v>
-          </cell>
-          <cell r="B32">
-            <v>0.21749999999999992</v>
-          </cell>
-          <cell r="D32">
-            <v>0.14499999999999993</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>3.3000000000000012</v>
-          </cell>
-          <cell r="B33">
-            <v>0.21090909090909082</v>
-          </cell>
-          <cell r="D33">
-            <v>0.14060606060606054</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>3.4000000000000012</v>
-          </cell>
-          <cell r="B34">
-            <v>0.2047058823529411</v>
-          </cell>
-          <cell r="D34">
-            <v>0.13647058823529407</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>3.5000000000000013</v>
-          </cell>
-          <cell r="B35">
-            <v>0.19885714285714276</v>
-          </cell>
-          <cell r="D35">
-            <v>0.13257142857142851</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>3.6000000000000014</v>
-          </cell>
-          <cell r="B36">
-            <v>0.19333333333333325</v>
-          </cell>
-          <cell r="D36">
-            <v>0.12888888888888883</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>3.7000000000000015</v>
-          </cell>
-          <cell r="B37">
-            <v>0.18810810810810802</v>
-          </cell>
-          <cell r="D37">
-            <v>0.12540540540540535</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>3.8000000000000016</v>
-          </cell>
-          <cell r="B38">
-            <v>0.18315789473684202</v>
-          </cell>
-          <cell r="D38">
-            <v>0.12210526315789468</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>3.9000000000000017</v>
-          </cell>
-          <cell r="B39">
-            <v>0.17846153846153837</v>
-          </cell>
-          <cell r="D39">
-            <v>0.11897435897435892</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>4.0000000000000018</v>
-          </cell>
-          <cell r="B40">
-            <v>0.1739999999999999</v>
-          </cell>
-          <cell r="D40">
-            <v>0.11599999999999994</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>4.1000000000000014</v>
-          </cell>
-          <cell r="B41">
-            <v>0.16975609756097554</v>
-          </cell>
-          <cell r="D41">
-            <v>0.11317073170731702</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>4.2000000000000011</v>
-          </cell>
-          <cell r="B42">
-            <v>0.16571428571428565</v>
-          </cell>
-          <cell r="D42">
-            <v>0.11047619047619044</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>4.3000000000000007</v>
-          </cell>
-          <cell r="B43">
-            <v>0.16186046511627902</v>
-          </cell>
-          <cell r="D43">
-            <v>0.10790697674418602</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>4.4000000000000004</v>
-          </cell>
-          <cell r="B44">
-            <v>0.15818181818181815</v>
-          </cell>
-          <cell r="D44">
-            <v>0.10545454545454543</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>4.5</v>
-          </cell>
-          <cell r="B45">
-            <v>0.15466666666666665</v>
-          </cell>
-          <cell r="D45">
-            <v>0.1031111111111111</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>4.5999999999999996</v>
-          </cell>
-          <cell r="B46">
-            <v>0.15130434782608695</v>
-          </cell>
-          <cell r="D46">
-            <v>0.10086956521739131</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>4.6999999999999993</v>
-          </cell>
-          <cell r="B47">
-            <v>0.14808510638297873</v>
-          </cell>
-          <cell r="D47">
-            <v>9.8723404255319155E-2</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>4.7999999999999989</v>
-          </cell>
-          <cell r="B48">
-            <v>0.14500000000000002</v>
-          </cell>
-          <cell r="D48">
-            <v>9.6666666666666679E-2</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>4.8999999999999986</v>
-          </cell>
-          <cell r="B49">
-            <v>0.14204081632653065</v>
-          </cell>
-          <cell r="D49">
-            <v>9.4693877551020433E-2</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>4.9999999999999982</v>
-          </cell>
-          <cell r="B50">
-            <v>0.13920000000000005</v>
-          </cell>
-          <cell r="D50">
-            <v>9.2800000000000035E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="14">
-        <row r="8">
-          <cell r="B8">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>1.44</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>2.4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Geom-Pisos"/>
-      <sheetName val="0-Matriz elemen"/>
-      <sheetName val="1-Matriz de rigidez"/>
-      <sheetName val="2-Matriz de masas"/>
-      <sheetName val="3-Matriz modal"/>
-      <sheetName val="4-Matriz espectral"/>
-      <sheetName val="5-gama"/>
-      <sheetName val="ModalxM"/>
-      <sheetName val="6-alpha"/>
-      <sheetName val="7-PERIODO"/>
-      <sheetName val="8-eta"/>
-      <sheetName val="9-GAMA"/>
-      <sheetName val="10-Desp+Deriva"/>
-      <sheetName val="11-Fmod+Cortante"/>
-      <sheetName val="12-Mvuelco2"/>
-      <sheetName val="14-Ksv"/>
-      <sheetName val="15-U descond"/>
-      <sheetName val="16-FUERZAS"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="4">
-          <cell r="M4">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="B1">
-            <v>71677.900502717777</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="3">
-          <cell r="B3">
-            <v>35</v>
-          </cell>
-          <cell r="C3">
-            <v>0</v>
-          </cell>
-          <cell r="D3">
-            <v>0</v>
-          </cell>
-          <cell r="E3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>0</v>
-          </cell>
-          <cell r="C4">
-            <v>50</v>
-          </cell>
-          <cell r="D4">
-            <v>0</v>
-          </cell>
-          <cell r="E4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>0</v>
-          </cell>
-          <cell r="C5">
-            <v>0</v>
-          </cell>
-          <cell r="D5">
-            <v>50</v>
-          </cell>
-          <cell r="E5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>0</v>
-          </cell>
-          <cell r="C6">
-            <v>0</v>
-          </cell>
-          <cell r="D6">
-            <v>0</v>
-          </cell>
-          <cell r="E6">
-            <v>50</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="3">
-          <cell r="B3">
-            <v>-9.0300000000000005E-2</v>
-          </cell>
-          <cell r="C3">
-            <v>-9.7199999999999995E-2</v>
-          </cell>
-          <cell r="D3">
-            <v>-8.8999999999999996E-2</v>
-          </cell>
-          <cell r="E3">
-            <v>-5.5399999999999998E-2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>-8.3799999999999999E-2</v>
-          </cell>
-          <cell r="C4">
-            <v>-3.1199999999999999E-2</v>
-          </cell>
-          <cell r="D4">
-            <v>6.3399999999999998E-2</v>
-          </cell>
-          <cell r="E4">
-            <v>8.9399999999999993E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>-6.9900000000000004E-2</v>
-          </cell>
-          <cell r="C5">
-            <v>5.9200000000000003E-2</v>
-          </cell>
-          <cell r="D5">
-            <v>6.1499999999999999E-2</v>
-          </cell>
-          <cell r="E5">
-            <v>-8.8499999999999995E-2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>-4.8800000000000003E-2</v>
-          </cell>
-          <cell r="C6">
-            <v>9.4399999999999998E-2</v>
-          </cell>
-          <cell r="D6">
-            <v>-8.1699999999999995E-2</v>
-          </cell>
-          <cell r="E6">
-            <v>4.4999999999999998E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>-9.0300000000000005E-2</v>
-          </cell>
-          <cell r="C10">
-            <v>-8.3799999999999999E-2</v>
-          </cell>
-          <cell r="D10">
-            <v>-6.9900000000000004E-2</v>
-          </cell>
-          <cell r="E10">
-            <v>-4.8800000000000003E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>-9.7199999999999995E-2</v>
-          </cell>
-          <cell r="C11">
-            <v>-3.1199999999999999E-2</v>
-          </cell>
-          <cell r="D11">
-            <v>5.9200000000000003E-2</v>
-          </cell>
-          <cell r="E11">
-            <v>9.4399999999999998E-2</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>-8.8999999999999996E-2</v>
-          </cell>
-          <cell r="C12">
-            <v>6.3399999999999998E-2</v>
-          </cell>
-          <cell r="D12">
-            <v>6.1499999999999999E-2</v>
-          </cell>
-          <cell r="E12">
-            <v>-8.1699999999999995E-2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>-5.5399999999999998E-2</v>
-          </cell>
-          <cell r="C13">
-            <v>8.9399999999999993E-2</v>
-          </cell>
-          <cell r="D13">
-            <v>-8.8499999999999995E-2</v>
-          </cell>
-          <cell r="E13">
-            <v>4.4999999999999998E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="B2">
-            <v>120</v>
-          </cell>
-          <cell r="C2">
-            <v>0</v>
-          </cell>
-          <cell r="D2">
-            <v>0</v>
-          </cell>
-          <cell r="E2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>0</v>
-          </cell>
-          <cell r="C3">
-            <v>1290</v>
-          </cell>
-          <cell r="D3">
-            <v>0</v>
-          </cell>
-          <cell r="E3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>0</v>
-          </cell>
-          <cell r="C4">
-            <v>0</v>
-          </cell>
-          <cell r="D4">
-            <v>3950</v>
-          </cell>
-          <cell r="E4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>0</v>
-          </cell>
-          <cell r="C5">
-            <v>0</v>
-          </cell>
-          <cell r="D5">
-            <v>0</v>
-          </cell>
-          <cell r="E5">
-            <v>7110</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="1">
-          <cell r="B1">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="1">
-          <cell r="B1">
-            <v>-3.1605000000000003</v>
-          </cell>
-          <cell r="C1">
-            <v>-4.1900000000000004</v>
-          </cell>
-          <cell r="D1">
-            <v>-3.4950000000000001</v>
-          </cell>
-          <cell r="E1">
-            <v>-2.44</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2">
-            <v>-3.4019999999999997</v>
-          </cell>
-          <cell r="C2">
-            <v>-1.5599999999999998</v>
-          </cell>
-          <cell r="D2">
-            <v>2.96</v>
-          </cell>
-          <cell r="E2">
-            <v>4.72</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>-3.1149999999999998</v>
-          </cell>
-          <cell r="C3">
-            <v>3.17</v>
-          </cell>
-          <cell r="D3">
-            <v>3.0750000000000002</v>
-          </cell>
-          <cell r="E3">
-            <v>-4.085</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>-1.9389999999999998</v>
-          </cell>
-          <cell r="C4">
-            <v>4.47</v>
-          </cell>
-          <cell r="D4">
-            <v>-4.4249999999999998</v>
-          </cell>
-          <cell r="E4">
-            <v>2.25</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="3">
-          <cell r="C3">
-            <v>-13.285500000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="4">
-          <cell r="C4">
-            <v>10.954000000000001</v>
-          </cell>
-          <cell r="F4">
-            <v>5.0608616154427036E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>4.7033153832356381E-3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>1.5375331303375316E-3</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="F7">
-            <v>8.5336932566558844E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="1">
-          <cell r="B1">
-            <v>-0.67236076991964044</v>
-          </cell>
-          <cell r="C1">
-            <v>0</v>
-          </cell>
-          <cell r="D1">
-            <v>0</v>
-          </cell>
-          <cell r="E1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2">
-            <v>0</v>
-          </cell>
-          <cell r="C2">
-            <v>1.2783611211634464E-2</v>
-          </cell>
-          <cell r="D2">
-            <v>0</v>
-          </cell>
-          <cell r="E2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>0</v>
-          </cell>
-          <cell r="C3">
-            <v>0</v>
-          </cell>
-          <cell r="D3">
-            <v>-1.468344139472342E-3</v>
-          </cell>
-          <cell r="E3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>0</v>
-          </cell>
-          <cell r="C4">
-            <v>0</v>
-          </cell>
-          <cell r="D4">
-            <v>0</v>
-          </cell>
-          <cell r="E4">
-            <v>3.0379947993694939E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="2">
-          <cell r="B2">
-            <v>6.0714177523743536E-2</v>
-          </cell>
-          <cell r="C2">
-            <v>-1.2425670097708699E-3</v>
-          </cell>
-          <cell r="D2">
-            <v>1.3068262841303842E-4</v>
-          </cell>
-          <cell r="E2">
-            <v>-1.6830491188506996E-5</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>5.634383251926587E-2</v>
-          </cell>
-          <cell r="C3">
-            <v>-3.9884866980299523E-4</v>
-          </cell>
-          <cell r="D3">
-            <v>-9.3093018442546479E-5</v>
-          </cell>
-          <cell r="E3">
-            <v>2.7159673506363275E-5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>4.6998017817382873E-2</v>
-          </cell>
-          <cell r="C4">
-            <v>7.5678978372876028E-4</v>
-          </cell>
-          <cell r="D4">
-            <v>-9.0303164577549037E-5</v>
-          </cell>
-          <cell r="E4">
-            <v>-2.688625397442002E-5</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>3.2811205572078457E-2</v>
-          </cell>
-          <cell r="C5">
-            <v>1.2067728983782933E-3</v>
-          </cell>
-          <cell r="D5">
-            <v>1.1996371619489033E-4</v>
-          </cell>
-          <cell r="E5">
-            <v>1.3670976597162722E-5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13">
-        <row r="17">
-          <cell r="H17">
-            <v>1023.4480201006024</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
-        <row r="3">
-          <cell r="F3">
-            <v>5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
